--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9420"/>
+    <workbookView windowWidth="23040" windowHeight="9420" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>子产品代码*</t>
   </si>
@@ -100,78 +100,6 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>子产品代码</t>
-  </si>
-  <si>
-    <t>子产品名称</t>
-  </si>
-  <si>
-    <t>子产品成立日期（YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>子产品募集金额</t>
-  </si>
-  <si>
-    <t>产品状态</t>
-  </si>
-  <si>
-    <t>产品系列</t>
-  </si>
-  <si>
-    <t>产品名称</t>
-  </si>
-  <si>
-    <t>产品简称</t>
-  </si>
-  <si>
-    <t>产品登记编码</t>
-  </si>
-  <si>
-    <t>产品主代码</t>
-  </si>
-  <si>
-    <t>募集开始日（YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>募集结束日（YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>产品募集金额</t>
-  </si>
-  <si>
-    <t>产品成立日期（YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>产品到期日期（YYYY-MM-DD)</t>
-  </si>
-  <si>
-    <t>募集方式</t>
-  </si>
-  <si>
-    <t>产品类型</t>
-  </si>
-  <si>
-    <t>发行方式</t>
-  </si>
-  <si>
-    <t>产品运作方式</t>
-  </si>
-  <si>
-    <t>是否是客户周期型产品</t>
-  </si>
-  <si>
-    <t>是否是分级产品</t>
-  </si>
-  <si>
-    <t>是否是指数型产品</t>
-  </si>
-  <si>
-    <t>投资性质</t>
-  </si>
-  <si>
-    <t>产品托管人名称</t>
   </si>
 </sst>
 </file>
@@ -836,7 +764,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -858,10 +786,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1220,16 +1157,16 @@
   <cols>
     <col min="1" max="1" width="16.6296296296296" customWidth="1"/>
     <col min="2" max="2" width="18.4537037037037" customWidth="1"/>
-    <col min="3" max="3" width="31.0925925925926" customWidth="1"/>
+    <col min="3" max="3" width="31.0925925925926" style="7" customWidth="1"/>
     <col min="6" max="6" width="9.81481481481481" customWidth="1"/>
     <col min="7" max="7" width="14.0925925925926" customWidth="1"/>
     <col min="8" max="8" width="16.8148148148148" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="29" customWidth="1"/>
-    <col min="11" max="11" width="27.3611111111111" customWidth="1"/>
+    <col min="10" max="10" width="29" style="7" customWidth="1"/>
+    <col min="11" max="11" width="27.3611111111111" style="7" customWidth="1"/>
     <col min="12" max="12" width="19.8148148148148" customWidth="1"/>
-    <col min="13" max="13" width="27.0925925925926" customWidth="1"/>
-    <col min="14" max="14" width="27.3611111111111" customWidth="1"/>
+    <col min="13" max="13" width="27.0925925925926" style="7" customWidth="1"/>
+    <col min="14" max="14" width="27.3611111111111" style="7" customWidth="1"/>
     <col min="15" max="15" width="22.2685185185185" customWidth="1"/>
     <col min="16" max="16" width="13.3611111111111" customWidth="1"/>
     <col min="17" max="17" width="19.7222222222222" customWidth="1"/>
@@ -1245,85 +1182,85 @@
   </cols>
   <sheetData>
     <row r="1" s="6" customFormat="1" ht="28.8" spans="1:27">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="U1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="V1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="W1" s="10" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Y1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="8" t="s">
+      <c r="Z1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AA1" s="10" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1334,23 +1271,23 @@
     </row>
   </sheetData>
   <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2 D3">
+      <formula1>"运行中,已到期,已销户"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2 Y3">
       <formula1>"固定收益类,权益类,商品及衍生类类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2 D3">
-      <formula1>"运行中,已到期,已销户"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2 O3">
       <formula1>"公募,私募"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2 P3">
+      <formula1>"净值型产品,现管类产品"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2 Q3">
+      <formula1>"开放式,封闭式"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:V2 W2 U3:V3 W3">
       <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2 P3">
-      <formula1>"净值型产品,现管类产品"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2 Q3">
-      <formula1>"开放式,封闭式"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:S2 R3:S3">
       <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
@@ -1375,154 +1312,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A1" s="1"/>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" ht="28.8" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="A4" s="1"/>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="A5" s="2"/>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="A6" s="2"/>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A7" s="1"/>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="A8" s="2"/>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="A9" s="2"/>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="A10" s="2"/>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="2" t="s">
-        <v>38</v>
-      </c>
+      <c r="A11" s="2"/>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="2" t="s">
-        <v>39</v>
-      </c>
+      <c r="A12" s="2"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" ht="28.8" spans="1:1">
-      <c r="A14" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" ht="28.8" spans="1:1">
-      <c r="A15" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3"/>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="A16" s="2"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="A17" s="2"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="A18" s="2"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" ht="15.15" spans="1:1">
-      <c r="A20" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" ht="15.15" spans="1:1">
-      <c r="A21" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" ht="15.15" spans="1:1">
-      <c r="A22" s="5" t="s">
-        <v>48</v>
-      </c>
+      <c r="A19" s="2"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="4"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
+      <c r="A23" s="2"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="A25" s="2"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="2" t="s">
-        <v>51</v>
-      </c>
+      <c r="A26" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
+      <formula1>"运行中,已到期,已销户"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25">
       <formula1>"固定收益类,权益类,商品及衍生类类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
-      <formula1>"运行中,已到期,已销户"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16">
       <formula1>"公募,私募"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17">
+      <formula1>"净值型产品,现管类产品"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
+      <formula1>"开放式,封闭式"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23 B21:B22">
       <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17">
-      <formula1>"净值型产品,现管类产品"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
-      <formula1>"开放式,封闭式"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19">
       <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9420" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9420"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1170,7 +1170,8 @@
     <col min="15" max="15" width="22.2685185185185" customWidth="1"/>
     <col min="16" max="16" width="13.3611111111111" customWidth="1"/>
     <col min="17" max="17" width="19.7222222222222" customWidth="1"/>
-    <col min="18" max="19" width="16.6296296296296" customWidth="1"/>
+    <col min="18" max="18" width="16.6296296296296" customWidth="1"/>
+    <col min="19" max="19" width="16.6296296296296" style="7" customWidth="1"/>
     <col min="20" max="20" width="17.7222222222222" customWidth="1"/>
     <col min="21" max="21" width="22.6296296296296" customWidth="1"/>
     <col min="22" max="22" width="24" customWidth="1"/>
@@ -1236,7 +1237,7 @@
       <c r="R1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="11" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="10" t="s">
@@ -1274,26 +1275,26 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2 D3">
       <formula1>"运行中,已到期,已销户"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2 O3">
+      <formula1>"公募,私募"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2 T3">
+      <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2 P3">
+      <formula1>"净值型产品,现管类产品"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2 Q3">
+      <formula1>"开放式,封闭式"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 R3">
+      <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2 Y3">
       <formula1>"固定收益类,权益类,商品及衍生类类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2 O3">
-      <formula1>"公募,私募"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2 P3">
-      <formula1>"净值型产品,现管类产品"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2 Q3">
-      <formula1>"开放式,封闭式"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:V2 W2 U3:V3 W3">
       <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:S2 R3:S3">
-      <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2 T3">
-      <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1368,13 +1369,13 @@
     <row r="19" spans="1:1">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" ht="15.15" spans="1:1">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" ht="15.15" spans="1:1">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" ht="15.15" spans="1:1">
       <c r="A22" s="5"/>
     </row>
     <row r="23" spans="1:1">
@@ -1391,26 +1392,26 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
       <formula1>"运行中,已到期,已销户"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16">
+      <formula1>"公募,私募"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20">
+      <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17">
+      <formula1>"净值型产品,现管类产品"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
+      <formula1>"开放式,封闭式"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19">
+      <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25">
       <formula1>"固定收益类,权益类,商品及衍生类类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16">
-      <formula1>"公募,私募"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17">
-      <formula1>"净值型产品,现管类产品"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
-      <formula1>"开放式,封闭式"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23 B21:B22">
       <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19">
-      <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20">
-      <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
@@ -695,7 +695,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="8">
+  <dataValidations count="9">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3">
       <formula1>"运行中,已到期,已销户"</formula1>
     </dataValidation>
@@ -714,11 +714,14 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3">
       <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y3">
-      <formula1>"固定收益类,权益类,商品及衍生类类,混合类"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3">
+      <formula1>"固定收益类,权益类,商品及衍生品类,混合类"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:W3">
       <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2">
+      <formula1>"固定收益类,权益类,商品及衍生品类,混合类"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25427"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bank\NJYH\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\IdeaProject2019\nanyin\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A34EE4F-0DEB-48F8-88C4-93CDD29E94AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9420"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>子产品代码*</t>
   </si>
@@ -105,25 +106,13 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>错误信息</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新人</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,14 +126,6 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -219,7 +200,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -257,9 +238,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -565,38 +543,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD9"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AA9"/>
+  <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="31.08984375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" customWidth="1"/>
-    <col min="7" max="7" width="14.08984375" customWidth="1"/>
-    <col min="8" max="8" width="16.81640625" customWidth="1"/>
+    <col min="1" max="1" width="16.59765625" customWidth="1"/>
+    <col min="2" max="2" width="18.46484375" customWidth="1"/>
+    <col min="3" max="3" width="31.06640625" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.796875" customWidth="1"/>
+    <col min="7" max="7" width="14.06640625" customWidth="1"/>
+    <col min="8" max="8" width="16.796875" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="29" style="7" customWidth="1"/>
-    <col min="11" max="11" width="27.36328125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="19.81640625" customWidth="1"/>
-    <col min="13" max="13" width="27.08984375" style="7" customWidth="1"/>
-    <col min="14" max="14" width="27.36328125" style="7" customWidth="1"/>
-    <col min="15" max="15" width="22.26953125" customWidth="1"/>
-    <col min="16" max="16" width="13.36328125" customWidth="1"/>
-    <col min="17" max="17" width="19.7265625" customWidth="1"/>
-    <col min="18" max="18" width="16.6328125" customWidth="1"/>
-    <col min="19" max="19" width="16.6328125" style="7" customWidth="1"/>
-    <col min="20" max="20" width="17.7265625" customWidth="1"/>
-    <col min="21" max="21" width="22.6328125" customWidth="1"/>
+    <col min="11" max="11" width="27.33203125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="19.796875" customWidth="1"/>
+    <col min="13" max="13" width="27.06640625" style="7" customWidth="1"/>
+    <col min="14" max="14" width="27.33203125" style="7" customWidth="1"/>
+    <col min="15" max="15" width="22.265625" customWidth="1"/>
+    <col min="16" max="16" width="13.33203125" customWidth="1"/>
+    <col min="17" max="17" width="19.73046875" customWidth="1"/>
+    <col min="18" max="18" width="16.59765625" customWidth="1"/>
+    <col min="19" max="19" width="16.59765625" style="7" customWidth="1"/>
+    <col min="20" max="20" width="17.73046875" customWidth="1"/>
+    <col min="21" max="21" width="22.59765625" customWidth="1"/>
     <col min="22" max="22" width="24" customWidth="1"/>
-    <col min="23" max="23" width="24.36328125" customWidth="1"/>
-    <col min="24" max="24" width="22.08984375" customWidth="1"/>
-    <col min="25" max="25" width="17.90625" customWidth="1"/>
-    <col min="28" max="28" width="18.7265625" customWidth="1"/>
-    <col min="29" max="29" width="17.36328125" customWidth="1"/>
+    <col min="23" max="23" width="24.33203125" customWidth="1"/>
+    <col min="24" max="24" width="22.06640625" customWidth="1"/>
+    <col min="25" max="25" width="17.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="6" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -678,50 +654,38 @@
       <c r="AA1" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC1" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD1" s="13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <dataValidations count="9">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3">
+  <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"运行中,已到期,已销户"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"公募,私募"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P3" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"净值型产品,现管类产品"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"开放式,封闭式"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y3" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"固定收益类,权益类,商品及衍生品类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:W3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:W3" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2">
-      <formula1>"固定收益类,权益类,商品及衍生品类,混合类"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -730,113 +694,113 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.26953125" customWidth="1"/>
+    <col min="1" max="1" width="24.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"运行中,已到期,已销户"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"公募,私募"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"净值型产品,现管类产品"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"开放式,封闭式"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19" xr:uid="{00000000-0002-0000-0100-000005000000}">
       <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25" xr:uid="{00000000-0002-0000-0100-000006000000}">
       <formula1>"固定收益类,权益类,商品及衍生类类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23 B21:B22">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23 B21:B22" xr:uid="{00000000-0002-0000-0100-000007000000}">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -846,11 +810,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\IdeaProject2019\nanyin\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A34EE4F-0DEB-48F8-88C4-93CDD29E94AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71206D25-7109-483A-9F22-54ACD53713A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>募集结束日期（YYYY-MM-DD)*</t>
   </si>
   <si>
-    <t>产品募集金额*</t>
-  </si>
-  <si>
     <t>产品成立日期（YYYY-MM-DD)*</t>
   </si>
   <si>
@@ -106,13 +103,17 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>总产品募集金额*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +130,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -200,7 +209,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -238,6 +247,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -545,34 +557,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultColWidth="8.53125" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.46484375" customWidth="1"/>
-    <col min="3" max="3" width="31.06640625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.796875" customWidth="1"/>
-    <col min="7" max="7" width="14.06640625" customWidth="1"/>
-    <col min="8" max="8" width="16.796875" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="31.109375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="29" style="7" customWidth="1"/>
     <col min="11" max="11" width="27.33203125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="19.796875" customWidth="1"/>
-    <col min="13" max="13" width="27.06640625" style="7" customWidth="1"/>
+    <col min="12" max="12" width="19.77734375" customWidth="1"/>
+    <col min="13" max="13" width="27.109375" style="7" customWidth="1"/>
     <col min="14" max="14" width="27.33203125" style="7" customWidth="1"/>
-    <col min="15" max="15" width="22.265625" customWidth="1"/>
+    <col min="15" max="15" width="22.21875" customWidth="1"/>
     <col min="16" max="16" width="13.33203125" customWidth="1"/>
-    <col min="17" max="17" width="19.73046875" customWidth="1"/>
-    <col min="18" max="18" width="16.59765625" customWidth="1"/>
-    <col min="19" max="19" width="16.59765625" style="7" customWidth="1"/>
-    <col min="20" max="20" width="17.73046875" customWidth="1"/>
-    <col min="21" max="21" width="22.59765625" customWidth="1"/>
+    <col min="17" max="17" width="19.77734375" customWidth="1"/>
+    <col min="18" max="18" width="16.5546875" customWidth="1"/>
+    <col min="19" max="19" width="16.5546875" style="7" customWidth="1"/>
+    <col min="20" max="20" width="17.77734375" customWidth="1"/>
+    <col min="21" max="21" width="22.5546875" customWidth="1"/>
     <col min="22" max="22" width="24" customWidth="1"/>
     <col min="23" max="23" width="24.33203125" customWidth="1"/>
-    <col min="24" max="24" width="22.06640625" customWidth="1"/>
-    <col min="25" max="25" width="17.9296875" customWidth="1"/>
+    <col min="24" max="24" width="22.109375" customWidth="1"/>
+    <col min="25" max="25" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -606,58 +618,58 @@
       <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="N1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="T1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="V1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="W1" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="X1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Z1" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="AA1" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="10" t="s">
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="D9" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -696,84 +708,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.265625" customWidth="1"/>
+    <col min="1" max="1" width="24.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
     </row>
   </sheetData>
@@ -812,7 +824,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71206D25-7109-483A-9F22-54ACD53713A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497077BC-22AB-4277-ACC9-73D3FE9C93D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,9 +75,6 @@
     <t>开放频率</t>
   </si>
   <si>
-    <t>固定持有天数</t>
-  </si>
-  <si>
     <t>产品运作方式*</t>
   </si>
   <si>
@@ -106,6 +103,10 @@
   </si>
   <si>
     <t>总产品募集金额*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>最低持有天数</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -209,7 +210,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -250,6 +251,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -619,7 +623,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>11</v>
@@ -639,37 +643,37 @@
       <c r="R1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="U1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="V1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="W1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="X1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Z1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="AA1" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="AA1" s="10" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="D9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25427"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JoyinWork\NYXP\tams\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{497077BC-22AB-4277-ACC9-73D3FE9C93D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>子产品代码*</t>
   </si>
@@ -85,9 +84,6 @@
   </si>
   <si>
     <t>是否是指数型产品*</t>
-  </si>
-  <si>
-    <t>产品业绩比较基准</t>
   </si>
   <si>
     <t>投资性质*</t>
@@ -113,7 +109,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -559,36 +555,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA9"/>
-  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:Z9"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
-    <col min="3" max="3" width="31.109375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="31.08984375" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" customWidth="1"/>
+    <col min="7" max="7" width="14.08984375" customWidth="1"/>
+    <col min="8" max="8" width="16.81640625" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="29" style="7" customWidth="1"/>
-    <col min="11" max="11" width="27.33203125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="19.77734375" customWidth="1"/>
-    <col min="13" max="13" width="27.109375" style="7" customWidth="1"/>
-    <col min="14" max="14" width="27.33203125" style="7" customWidth="1"/>
-    <col min="15" max="15" width="22.21875" customWidth="1"/>
-    <col min="16" max="16" width="13.33203125" customWidth="1"/>
-    <col min="17" max="17" width="19.77734375" customWidth="1"/>
-    <col min="18" max="18" width="16.5546875" customWidth="1"/>
-    <col min="19" max="19" width="16.5546875" style="7" customWidth="1"/>
-    <col min="20" max="20" width="17.77734375" customWidth="1"/>
-    <col min="21" max="21" width="22.5546875" customWidth="1"/>
+    <col min="11" max="11" width="27.36328125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="19.81640625" customWidth="1"/>
+    <col min="13" max="13" width="27.08984375" style="7" customWidth="1"/>
+    <col min="14" max="14" width="27.36328125" style="7" customWidth="1"/>
+    <col min="15" max="15" width="22.1796875" customWidth="1"/>
+    <col min="16" max="16" width="13.36328125" customWidth="1"/>
+    <col min="17" max="17" width="19.81640625" customWidth="1"/>
+    <col min="18" max="18" width="16.54296875" customWidth="1"/>
+    <col min="19" max="19" width="16.54296875" style="7" customWidth="1"/>
+    <col min="20" max="20" width="17.81640625" customWidth="1"/>
+    <col min="21" max="21" width="22.54296875" customWidth="1"/>
     <col min="22" max="22" width="24" customWidth="1"/>
-    <col min="23" max="23" width="24.33203125" customWidth="1"/>
-    <col min="24" max="24" width="22.109375" customWidth="1"/>
-    <col min="25" max="25" width="17.88671875" customWidth="1"/>
+    <col min="23" max="23" width="24.36328125" customWidth="1"/>
+    <col min="24" max="24" width="17.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="6" customFormat="1" ht="42" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -623,7 +618,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M1" s="11" t="s">
         <v>11</v>
@@ -644,7 +639,7 @@
         <v>16</v>
       </c>
       <c r="S1" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T1" s="10" t="s">
         <v>17</v>
@@ -658,7 +653,7 @@
       <c r="W1" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="10" t="s">
         <v>21</v>
       </c>
       <c r="Y1" s="10" t="s">
@@ -667,40 +662,37 @@
       <c r="Z1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="10" t="s">
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D9" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3">
       <formula1>"运行中,已到期,已销户"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O3">
       <formula1>"公募,私募"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T3">
       <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P3" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P3">
       <formula1>"净值型产品,现管类产品"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q3">
       <formula1>"开放式,封闭式"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R3">
       <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y2:Y3" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3">
       <formula1>"固定收益类,权益类,商品及衍生品类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:W3" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:W3">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -710,11 +702,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.21875" customWidth="1"/>
+    <col min="1" max="1" width="24.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -795,28 +787,28 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
       <formula1>"运行中,已到期,已销户"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16">
       <formula1>"公募,私募"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B20">
       <formula1>"开放式净值型,开放式非净值型,封闭式净值型,封闭式非净值型"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B17">
       <formula1>"净值型产品,现管类产品"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18">
       <formula1>"开放式,封闭式"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19" xr:uid="{00000000-0002-0000-0100-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B19">
       <formula1>"日开,频率在半年（不含）以内,频率在半年以上"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25" xr:uid="{00000000-0002-0000-0100-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B25">
       <formula1>"固定收益类,权益类,商品及衍生类类,混合类"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23 B21:B22" xr:uid="{00000000-0002-0000-0100-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B23 B21:B22">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -826,9 +818,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\nyxp\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\NY\tams-disclosure-parent\tams-disclosure\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="12580"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23265" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
     <t>子产品名称*</t>
   </si>
   <si>
-    <t>子产品成立日期（YYYY-MM-DD)*</t>
-  </si>
-  <si>
     <t>产品状态*</t>
   </si>
   <si>
@@ -48,18 +45,6 @@
   </si>
   <si>
     <t>产品主代码*</t>
-  </si>
-  <si>
-    <t>募集起始日期（YYYY-MM-DD)*</t>
-  </si>
-  <si>
-    <t>募集结束日期（YYYY-MM-DD)*</t>
-  </si>
-  <si>
-    <t>产品成立日期（YYYY-MM-DD)*</t>
-  </si>
-  <si>
-    <t>产品到期日期（YYYY-MM-DD)*</t>
   </si>
   <si>
     <t>募集方式*</t>
@@ -103,6 +88,26 @@
   </si>
   <si>
     <t>最低持有天数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>子产品成立日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>募集起始日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>募集结束日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品成立日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品到期日期（YYYY/MM/DD)*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -557,33 +562,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Z9"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="31.08984375" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.81640625" customWidth="1"/>
-    <col min="7" max="7" width="14.08984375" customWidth="1"/>
-    <col min="8" max="8" width="16.81640625" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
+    <col min="3" max="3" width="31.125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.875" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
     <col min="10" max="10" width="29" style="7" customWidth="1"/>
-    <col min="11" max="11" width="27.36328125" style="7" customWidth="1"/>
-    <col min="12" max="12" width="19.81640625" customWidth="1"/>
-    <col min="13" max="13" width="27.08984375" style="7" customWidth="1"/>
-    <col min="14" max="14" width="27.36328125" style="7" customWidth="1"/>
-    <col min="15" max="15" width="22.1796875" customWidth="1"/>
-    <col min="16" max="16" width="13.36328125" customWidth="1"/>
-    <col min="17" max="17" width="19.81640625" customWidth="1"/>
-    <col min="18" max="18" width="16.54296875" customWidth="1"/>
-    <col min="19" max="19" width="16.54296875" style="7" customWidth="1"/>
-    <col min="20" max="20" width="17.81640625" customWidth="1"/>
-    <col min="21" max="21" width="22.54296875" customWidth="1"/>
+    <col min="11" max="11" width="27.375" style="7" customWidth="1"/>
+    <col min="12" max="12" width="19.875" customWidth="1"/>
+    <col min="13" max="13" width="27.125" style="7" customWidth="1"/>
+    <col min="14" max="14" width="27.375" style="7" customWidth="1"/>
+    <col min="15" max="15" width="22.125" customWidth="1"/>
+    <col min="16" max="16" width="13.375" customWidth="1"/>
+    <col min="17" max="17" width="19.875" customWidth="1"/>
+    <col min="18" max="18" width="16.5" customWidth="1"/>
+    <col min="19" max="19" width="16.5" style="7" customWidth="1"/>
+    <col min="20" max="20" width="17.875" customWidth="1"/>
+    <col min="21" max="21" width="22.5" customWidth="1"/>
     <col min="22" max="22" width="24" customWidth="1"/>
-    <col min="23" max="23" width="24.36328125" customWidth="1"/>
-    <col min="24" max="24" width="17.90625" customWidth="1"/>
+    <col min="23" max="23" width="24.375" customWidth="1"/>
+    <col min="24" max="24" width="17.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="6" customFormat="1" ht="42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="6" customFormat="1" ht="27" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -591,81 +596,81 @@
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="J1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="P1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="Q1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="11" t="s">
+      <c r="R1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="S1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="U1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="V1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="W1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="X1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="T1" s="10" t="s">
+      <c r="Y1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="Z1" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="12" t="s">
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.15">
+      <c r="D9" t="s">
         <v>19</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D9" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -704,84 +709,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.1796875" customWidth="1"/>
+    <col min="1" max="1" width="24.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="1"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="1"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="2"/>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="2"/>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="2"/>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="2"/>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="2"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="2"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="2"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="2"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="2"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="4"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="2"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" s="2"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" s="2"/>
     </row>
   </sheetData>
@@ -820,7 +825,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
@@ -211,7 +211,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -239,15 +239,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -255,6 +249,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -566,16 +569,16 @@
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
     <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="3" width="31.125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="31.125" style="14" customWidth="1"/>
     <col min="6" max="6" width="9.875" customWidth="1"/>
     <col min="7" max="7" width="14.125" customWidth="1"/>
     <col min="8" max="8" width="16.875" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="29" style="7" customWidth="1"/>
-    <col min="11" max="11" width="27.375" style="7" customWidth="1"/>
+    <col min="10" max="10" width="29" style="14" customWidth="1"/>
+    <col min="11" max="11" width="27.375" style="14" customWidth="1"/>
     <col min="12" max="12" width="19.875" customWidth="1"/>
-    <col min="13" max="13" width="27.125" style="7" customWidth="1"/>
-    <col min="14" max="14" width="27.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="27.125" style="14" customWidth="1"/>
+    <col min="14" max="14" width="27.375" style="14" customWidth="1"/>
     <col min="15" max="15" width="22.125" customWidth="1"/>
     <col min="16" max="16" width="13.375" customWidth="1"/>
     <col min="17" max="17" width="19.875" customWidth="1"/>
@@ -595,76 +598,76 @@
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="R1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="14" t="s">
+      <c r="S1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="12" t="s">
+      <c r="U1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="12" t="s">
+      <c r="V1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="W1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="Z1" s="9" t="s">
         <v>18</v>
       </c>
     </row>

--- a/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
+++ b/tams-disclosure-parent/tams-disclosure/src/main/resources/tpl/ProdInfo001.xlsx
@@ -35,9 +35,6 @@
     <t>产品系列*</t>
   </si>
   <si>
-    <t>产品名称*</t>
-  </si>
-  <si>
     <t>产品简称*</t>
   </si>
   <si>
@@ -108,6 +105,10 @@
   </si>
   <si>
     <t>产品到期日期（YYYY/MM/DD)*</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品全称*</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -599,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>2</v>
@@ -608,72 +609,72 @@
         <v>3</v>
       </c>
       <c r="F1" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L1" s="11" t="s">
+      <c r="P1" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="S1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="R1" s="9" t="s">
+      <c r="T1" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="T1" s="9" t="s">
+      <c r="U1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="W1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="X1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="Y1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Z1" s="9" t="s">
         <v>17</v>
-      </c>
-      <c r="Z1" s="9" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.15">
       <c r="D9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
